--- a/Lucknow-June-2025.xlsx
+++ b/Lucknow-June-2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>Sr. No</t>
   </si>
@@ -94,28 +94,22 @@
     <t>Profit %</t>
   </si>
   <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>Lucknow</t>
   </si>
   <si>
     <t>June</t>
   </si>
   <si>
-    <t>MH02ER8597</t>
-  </si>
-  <si>
-    <t>MH02ER8935</t>
-  </si>
-  <si>
     <t>MH43BP4034</t>
   </si>
   <si>
-    <t>Crysta</t>
-  </si>
-  <si>
     <t>ETIOS</t>
   </si>
   <si>
-    <t>-</t>
+    <t>30/09/2021</t>
   </si>
 </sst>
 </file>
@@ -473,10 +467,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z4"/>
+  <dimension ref="A1:AA2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -555,40 +549,43 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>2025</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" t="s">
         <v>31</v>
       </c>
-      <c r="G2">
-        <v>43554</v>
-      </c>
       <c r="H2">
-        <v>127905</v>
+        <v>270120</v>
       </c>
       <c r="I2">
-        <v>131995</v>
+        <v>274890</v>
       </c>
       <c r="J2">
-        <v>4090</v>
+        <v>4770</v>
       </c>
       <c r="K2">
-        <v>4090</v>
+        <v>4770</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -597,13 +594,13 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>4090</v>
+        <v>4770</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>149399</v>
+        <v>160212</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -612,187 +609,27 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>149399</v>
+        <v>160212</v>
       </c>
       <c r="T2">
-        <v>32015</v>
+        <v>24762</v>
       </c>
       <c r="U2">
-        <v>39460</v>
+        <v>4040</v>
       </c>
       <c r="V2">
-        <v>15809</v>
+        <v>16954</v>
       </c>
       <c r="W2">
         <v>0</v>
       </c>
       <c r="X2">
-        <v>87284</v>
+        <v>45756</v>
       </c>
       <c r="Y2">
-        <v>62115</v>
+        <v>114456</v>
       </c>
       <c r="Z2">
-        <v>41.58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26">
-      <c r="A3">
-        <v>264</v>
-      </c>
-      <c r="B3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3">
-        <v>2025</v>
-      </c>
-      <c r="E3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3">
-        <v>43579</v>
-      </c>
-      <c r="H3">
-        <v>109221</v>
-      </c>
-      <c r="I3">
-        <v>114127</v>
-      </c>
-      <c r="J3">
-        <v>4906</v>
-      </c>
-      <c r="K3">
-        <v>4906</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>4906</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>195017</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>195017</v>
-      </c>
-      <c r="T3">
-        <v>35540</v>
-      </c>
-      <c r="U3">
-        <v>2160</v>
-      </c>
-      <c r="V3">
-        <v>20637</v>
-      </c>
-      <c r="W3">
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <v>58337</v>
-      </c>
-      <c r="Y3">
-        <v>136680</v>
-      </c>
-      <c r="Z3">
-        <v>70.09</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26">
-      <c r="A4">
-        <v>265</v>
-      </c>
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4">
-        <v>2025</v>
-      </c>
-      <c r="E4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H4">
-        <v>270120</v>
-      </c>
-      <c r="I4">
-        <v>274890</v>
-      </c>
-      <c r="J4">
-        <v>4770</v>
-      </c>
-      <c r="K4">
-        <v>4770</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>4770</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>160212</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>160212</v>
-      </c>
-      <c r="T4">
-        <v>24762</v>
-      </c>
-      <c r="U4">
-        <v>4040</v>
-      </c>
-      <c r="V4">
-        <v>16954</v>
-      </c>
-      <c r="W4">
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <v>45756</v>
-      </c>
-      <c r="Y4">
-        <v>114456</v>
-      </c>
-      <c r="Z4">
         <v>71.44</v>
       </c>
     </row>
